--- a/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-01_Contexto_SWOT_PESTEL.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-01_Contexto_SWOT_PESTEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGA_Sistema-de-gestao-ambiental\Registos_SGA_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9187A924-4AC8-474B-B08E-539F2DB1B96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BDB234-F175-4306-8FBC-513A9A3A7477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
